--- a/artfynd/A 59057-2025 artfynd.xlsx
+++ b/artfynd/A 59057-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135437324</v>
+        <v>135524727</v>
       </c>
       <c r="B2" t="n">
-        <v>58812</v>
+        <v>58415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>102999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,29 +708,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dombäcksviken, Dombäcksviken, Ång</t>
+          <t>Husum Dombäcksviken, Husum Dombäcksviken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706897</v>
+        <v>706891</v>
       </c>
       <c r="R2" t="n">
-        <v>7029657</v>
+        <v>7029662</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,6 +788,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135437324</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58812</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dombäcksviken, Dombäcksviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>706897</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7029657</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grundsunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Camilla Pakka</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Camilla Pakka</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59057-2025 artfynd.xlsx
+++ b/artfynd/A 59057-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135524727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135437324</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59057-2025 artfynd.xlsx
+++ b/artfynd/A 59057-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135524727</v>
       </c>
       <c r="B2" t="n">
-        <v>58415</v>
+        <v>58420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135437324</v>
       </c>
       <c r="B3" t="n">
-        <v>58812</v>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59057-2025 artfynd.xlsx
+++ b/artfynd/A 59057-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135524727</v>
       </c>
       <c r="B2" t="n">
-        <v>58420</v>
+        <v>58422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135437324</v>
       </c>
       <c r="B3" t="n">
-        <v>58817</v>
+        <v>58819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
